--- a/product_order_forms/034_order_and_pickup_form--product_order_forms.xlsx
+++ b/product_order_forms/034_order_and_pickup_form--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'8am-12pm',_'value':_'8am-12pm'}</t>
+          <t>8am-12pm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '8am-12pm', 'value': '8am-12pm'}</t>
+          <t>8am-12pm</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'12pm-4pm',_'value':_'12pm-4pm'}</t>
+          <t>12pm-4pm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '12pm-4pm', 'value': '12pm-4pm'}</t>
+          <t>12pm-4pm</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'4pm-8pm',_'value':_'4pm-8pm'}</t>
+          <t>4pm-8pm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '4pm-8pm', 'value': '4pm-8pm'}</t>
+          <t>4pm-8pm</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'product_1',_'value':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Product 1', 'value': 'product_1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'product_2',_'value':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Product 2', 'value': 'product_2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_3',_'value':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product 3', 'value': 'product_3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
